--- a/parts_list.xlsx
+++ b/parts_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\GitHub\RC_Car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938ADBB3-7944-44C5-954E-E764EBCC2C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49399AE-E590-4549-96BC-7562D7D26009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{DFB2C8BE-003C-4554-867F-6DFF130D1313}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{DFB2C8BE-003C-4554-867F-6DFF130D1313}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,6 +209,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -227,19 +235,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -656,7 +667,7 @@
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="2">
@@ -683,7 +694,7 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="2">
@@ -737,7 +748,7 @@
       <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="2">
@@ -764,7 +775,7 @@
       <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="2">
@@ -791,7 +802,7 @@
       <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="2">
@@ -892,6 +903,13 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{E9E33779-E925-404F-8734-B8DC17057FBC}"/>
+    <hyperlink ref="D6" r:id="rId2" xr:uid="{E4E77FFD-B479-42EA-A828-FCDC7DF31EFB}"/>
+    <hyperlink ref="D8" r:id="rId3" xr:uid="{70F9A727-B0C1-4194-B37B-DD5CFE0902BA}"/>
+    <hyperlink ref="D9" r:id="rId4" xr:uid="{B54EC77E-3914-4969-B64B-2C4873B66166}"/>
+    <hyperlink ref="D10" r:id="rId5" xr:uid="{5E7439DB-C39F-42DC-B4CF-B16D048B7E6A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>